--- a/experiment/HAT_2CH_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/HAT_2CH_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.65</v>
+        <v>27.64</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7682</v>
+        <v>0.7681</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.87</v>
+        <v>26.89</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>23.94</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6926</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.85</v>
+        <v>23.98</v>
       </c>
       <c r="C5" t="n">
-        <v>0.844</v>
+        <v>0.8458</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>28.29</v>
       </c>
       <c r="C6" t="n">
-        <v>0.953</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.6</v>
+        <v>22.62</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6313</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.64</v>
+        <v>29.65</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8636</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>21.6</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6705</v>
+        <v>0.6696</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.73</v>
+        <v>33.81</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9252</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.57</v>
+        <v>27.54</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8932</v>
+        <v>0.8925999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>18.05</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7967</v>
+        <v>0.7982</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         <v>23.98</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7393</v>
+        <v>0.7397</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +611,7 @@
         <v>29.67</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8419</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.42</v>
+        <v>22.41</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6927</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +637,7 @@
         <v>26.38</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7427</v>
+        <v>0.7429</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.5</v>
+        <v>30.42</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9161</v>
+        <v>0.9151</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.81</v>
+        <v>25.82</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8313</v>
+        <v>0.8316</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.4</v>
+        <v>26.41</v>
       </c>
       <c r="C19" t="n">
-        <v>0.715</v>
+        <v>0.7151</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8225</v>
+        <v>0.8231000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.75</v>
+        <v>29.76</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7867</v>
+        <v>0.7868000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +728,7 @@
         <v>26.13</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7635</v>
+        <v>0.7631</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9182</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.99</v>
+        <v>20.03</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6584</v>
+        <v>0.6607</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.51</v>
+        <v>32.6</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9053</v>
+        <v>0.9064</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28.15</v>
+        <v>28.11</v>
       </c>
       <c r="C27" t="n">
-        <v>0.708</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.47</v>
+        <v>28.5</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8011</v>
+        <v>0.8016</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8792</v>
+        <v>0.8782</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27.5</v>
+        <v>27.49</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8763</v>
+        <v>0.8764</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.61</v>
+        <v>24.65</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8108</v>
+        <v>0.8116</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>24.35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7958</v>
+        <v>0.7959000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.34</v>
+        <v>29.3</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8613</v>
+        <v>0.8606</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.48</v>
+        <v>27.46</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8129</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>23.09</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5886</v>
+        <v>0.5888</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.37</v>
+        <v>29.29</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8838</v>
+        <v>0.8831</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.87</v>
+        <v>28.83</v>
       </c>
       <c r="C37" t="n">
-        <v>0.888</v>
+        <v>0.8874</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.56</v>
+        <v>26.57</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8037</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.09</v>
+        <v>26.98</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6833</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>23.18</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7534</v>
+        <v>0.7528</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.39</v>
+        <v>27.33</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9443</v>
+        <v>0.944</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.53</v>
+        <v>26.56</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.8862</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.84</v>
+        <v>28.79</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8877</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.72</v>
+        <v>32.79</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9375</v>
+        <v>0.9377</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.64</v>
+        <v>31.83</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8688</v>
+        <v>0.8709</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.29</v>
+        <v>24.26</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7195</v>
+        <v>0.7239</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.66</v>
+        <v>23.65</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7622</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.94</v>
+        <v>21.99</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7753</v>
+        <v>0.7773</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.27</v>
+        <v>20.26</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8169</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.64</v>
+        <v>23.66</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7568</v>
+        <v>0.7572</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.38</v>
+        <v>25.37</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7771</v>
+        <v>0.7766999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -1105,7 +1105,7 @@
         <v>27.49</v>
       </c>
       <c r="C52" t="n">
-        <v>0.851</v>
+        <v>0.8511</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.92</v>
+        <v>28.95</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9099</v>
+        <v>0.9101</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.52</v>
+        <v>22.51</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7357</v>
+        <v>0.7354000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6573</v>
+        <v>0.6569</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>33.78</v>
+        <v>33.9</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9509</v>
+        <v>0.9510999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.1</v>
+        <v>25.09</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7883</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.22</v>
+        <v>31.23</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8999</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.95</v>
+        <v>25.97</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8618</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.25</v>
+        <v>22.32</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7709</v>
+        <v>0.7729</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.64</v>
+        <v>22.65</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5752</v>
+        <v>0.5754</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.79</v>
+        <v>24.7</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7642</v>
+        <v>0.7599</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.82</v>
+        <v>21.91</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8155</v>
+        <v>0.8178</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.49</v>
+        <v>22.5</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6223</v>
+        <v>0.6221</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         <v>26.57</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7851</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="66">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.45</v>
+        <v>25.44</v>
       </c>
       <c r="C66" t="n">
         <v>0.7255</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.22</v>
+        <v>22.2</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6425</v>
+        <v>0.6409</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19.86</v>
+        <v>19.84</v>
       </c>
       <c r="C68" t="n">
-        <v>0.884</v>
+        <v>0.8846000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.38</v>
+        <v>30.47</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8891</v>
+        <v>0.8902</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         <v>24.84</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7579</v>
+        <v>0.7578</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>22.21</v>
       </c>
       <c r="C71" t="n">
-        <v>0.6005</v>
+        <v>0.6002</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.16</v>
+        <v>28.15</v>
       </c>
       <c r="C72" t="n">
-        <v>0.677</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="73">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.17</v>
+        <v>20.15</v>
       </c>
       <c r="C74" t="n">
-        <v>0.577</v>
+        <v>0.5759</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.98</v>
+        <v>23.97</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7295</v>
+        <v>0.7274</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.81</v>
+        <v>31.8</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8881</v>
+        <v>0.8882</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.24</v>
+        <v>23.21</v>
       </c>
       <c r="C77" t="n">
-        <v>0.748</v>
+        <v>0.7483</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.73</v>
+        <v>22.74</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6774</v>
+        <v>0.6773</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>27.45</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7764</v>
+        <v>0.7758</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         <v>25.49</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6989</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.7</v>
+        <v>35.75</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9534</v>
+        <v>0.9537</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.94</v>
+        <v>38.08</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9738</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="83">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.84</v>
+        <v>32.79</v>
       </c>
       <c r="C83" t="n">
         <v>0.9414</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.36</v>
+        <v>22.3</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7094</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.79</v>
+        <v>28.8</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8142</v>
+        <v>0.8144</v>
       </c>
     </row>
     <row r="86">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.4</v>
+        <v>28.41</v>
       </c>
       <c r="C86" t="n">
         <v>0.9045</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.41</v>
+        <v>30.52</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8872</v>
+        <v>0.8874</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.88</v>
+        <v>27.89</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8875</v>
+        <v>0.8873</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.82</v>
+        <v>19.79</v>
       </c>
       <c r="C89" t="n">
-        <v>0.572</v>
+        <v>0.5692</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.78</v>
+        <v>26.77</v>
       </c>
       <c r="C90" t="n">
-        <v>0.721</v>
+        <v>0.7197</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.81</v>
+        <v>37.98</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9757</v>
+        <v>0.9762</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>23.89</v>
+        <v>23.92</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6768</v>
+        <v>0.6774</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>18.89</v>
+        <v>18.93</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6565</v>
+        <v>0.6586</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>29.74</v>
+        <v>29.79</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9323</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="95">
@@ -1664,7 +1664,7 @@
         <v>27.22</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7864</v>
+        <v>0.7861</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4438</v>
+        <v>0.4405</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25.41</v>
+        <v>25.33</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8737</v>
+        <v>0.8722</v>
       </c>
     </row>
     <row r="98">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.76</v>
+        <v>20.77</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5416</v>
+        <v>0.5414</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.16</v>
+        <v>26.23</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8069</v>
+        <v>0.8085</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.48</v>
+        <v>26.47</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7546</v>
+        <v>0.7544999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.16</v>
+        <v>26.17</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7886</v>
+        <v>0.7887</v>
       </c>
     </row>
   </sheetData>
